--- a/MUQABIL_Practice_History_Test_Candidate_2026-10-13.xlsx
+++ b/MUQABIL_Practice_History_Test_Candidate_2026-10-13.xlsx
@@ -425,7 +425,7 @@
         <v>Export Date</v>
       </c>
       <c r="B3" t="str">
-        <v>10/13/2026, 2:42:44 PM</v>
+        <v>10/13/2026, 4:25:12 PM</v>
       </c>
     </row>
     <row r="4">
